--- a/LISTAS_ORDENADAS/MA/Tarugos/TARUGO ESPIGA DISMAY.xlsx
+++ b/LISTAS_ORDENADAS/MA/Tarugos/TARUGO ESPIGA DISMAY.xlsx
@@ -1151,14 +1151,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="17" t="n">
-        <v>45203.5525215741</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="18">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -1204,8 +1200,6 @@
       </c>
       <c r="E11" s="14" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
@@ -1213,12 +1207,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
@@ -1226,15 +1214,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
     <row r="31" ht="18" customHeight="1" s="18">
       <c r="A31" s="15" t="inlineStr">
         <is>
@@ -1324,10 +1303,6 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
@@ -1335,14 +1310,6 @@
         </is>
       </c>
     </row>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
     <row r="50" ht="15.75" customHeight="1" s="18">
       <c r="A50" s="4" t="n"/>
     </row>
@@ -1351,16 +1318,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="A36:D36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
